--- a/docs/triton-learning/cards/triton-lesson-07-extern-functions-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-07-extern-functions-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -55,68 +55,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 接口空壳 → get_module_map → 后端实现</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 接口模块与 dtype 查表</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 的 kernel 用 tl.load 从 fp16 张量读出 x，然后直接调用 libdevice.erf(x)。这次编译会在哪一步失败，报什么错？应该怎样修改，结果又怎样写回 fp16 的输出？</t>
+          <t xml:space="preserve">给一个基于 Triton 3.7.1 的新后端加 libdevice 支持时，用户的 kernel 在 y = libdevice.asin(x) 的下一行 tl.store 处报错：cannot convert None of type NoneType to tensor。libdevice 那一行本身没有报错。最可能的原因是什么？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：在按实参 dtype 查表时失败，报 KeyError: (triton.language.float16)；先把 x 显式转成 fp32 再调用。
-• [T#B#表的含义]：后端实现里的每个 libdevice 函数是一张表：参数 dtype 元组对应符号名和返回 dtype。erf 的表只有 fp32 对 __nv_erff、fp64 对 __nv_erf 两项。
-• [T#B#查表]：extern_elementwise 在编译期用实参的 dtype 查表：查到就生成一条带 symbol 的 tt.extern_elementwise，查不到就报错，不做隐式类型提升。
-• [T#B#修改]：写成 libdevice.erf(x.to(tl.float32))。结果是 fp32，tl.store 写入 fp16 指针时会自动转成指针的元素类型。
-• [T#B#多个参数]：pow、atan2 这类函数的键是所有参数 dtype 组成的元组。pow 的 x 是 bf16、y 是 fp32 时同样报 KeyError，把 x 转成 fp32 后选中 __nv_powf。
-[T#B,!c47f17#边界]：tl.math 的函数同样只接受 fp32 和 fp64。源码写明了理由：很多加速器不支持半精度的数学运算，应让用户知情并显式转换。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dtype 元组查表；半精度先转 fp32</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · dtype 元组查表；半精度先转 fp32</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">给一个新的 Triton 后端加 libdevice 支持时，用户的 kernel 在 y = libdevice.asin(x) 的下一行 tl.store 处报错：cannot convert None of type NoneType to tensor。libdevice 那一行本身没有报错。最可能的原因是什么？</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：后端的 get_module_map() 没有生效，kernel 调到了接口模块里的空壳函数。
 • [T#B#现象]：空壳函数被调用后静默返回 None，错误要等下一次使用这个结果时才暴露，所以指向 tl.store，看上去和 libdevice 无关。
 • [T#B#对比]：映射生效但缺少函数时，报的是 AttributeError，消息里写的是替换后的模块名，可以借此确认替换已经发生。</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">空壳返回 None → 下一行才报错</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 空壳返回 None → 下一行才报错</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton 3.7.1、NVIDIA 后端：kernel 对长度为 BLOCK_SIZE 的 fp32 块 x 调用 libdevice.asin(x)，num_warps 为 W，每个 warp 有 32 个线程。从 TTGIR 降级到最终 PTX 的过程中，针对一个线程，__nv_asinf 的声明、调用、定义和函数体各有几份？为什么最终的 PTX 里没有 call？</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 接口模块与 dtype 查表</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1、NVIDIA 后端：kernel 对长度为 BLOCK_SIZE 的 fp32 块 x 调用 libdevice.asin(x)，fp32 版本的库函数符号是 __nv_asinf。num_warps 为 W，每个 warp 有 32 个线程，BLOCK_SIZE 是 32 × W 的整数倍。从 TTGIR 降级到最终 PTX 的过程中，针对一个线程，__nv_asinf 的声明、调用、定义和函数体各有几份？为什么最终的 PTX 里没有 call？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：每个线程持有 E = BLOCK_SIZE ÷ (32 × W) 个元素：声明 1 条，调用 E 次，链接后定义 1 份，内联后函数体 E 份，call 为 0。
 • [T#B#逐元素调用]：libdevice 函数的签名是标量的。降级到 LLVM IR 时，编译器替一个线程写程序，它持有几个元素就生成几次标量调用；整个模块只需要一条声明。
@@ -126,179 +99,177 @@
 [T#B,!c47f17#边界]：代码量随 E 线性增长。指针按 16 字节特化后，访存会合并成更宽的指令，但数学计算仍然是每个元素一份。</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 声明 · E 调用 · 1 定义 · E 份函数体 · 0 call</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 编译器前置与逐元素调用、链接、内联</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1 的 NVIDIA 后端会把 libdevice 库文件链接进 kernel。编译缓存怎样感知库文件的变化？由此，库路径写错时，错误会出现在编译的哪个阶段？</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：库文件的内容哈希计入编译缓存键，换一份库就会重新编译；也因为算缓存键时就要读文件，路径不存在时立刻报 FileNotFoundError，比生成任何 IR 都早。
+• [T#B#例子]：官方教程第二段拼出的自定义路径，假设脚本位于 Triton 源码树的 python/tutorials/ 下；在 pip 安装的环境里这个路径不存在，就会撞上这个错误。pip 环境里的自带库在已安装 triton 包下的 backends/nvidia/lib/libdevice.10.bc。
+• [T#B#延伸]：不显式指定时用 wheel 自带的这份库，可以用环境变量 TRITON_LIBDEVICE_PATH 或启动参数 extern_libs 替换。
+[T#B,!c47f17#边界]：这是 NVIDIA 后端的做法；其他后端是否把库的内容计入缓存键，取决于各自的实现。</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 声明 · E 调用 · 1 定义 · E 份函数体 · 0 call</t>
+          <t xml:space="preserve">库内容哈希进缓存键 → 换库重编、坏路径最早报错</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 1 声明 · E 调用 · 1 定义 · E 份函数体 · 0 call</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 编译器前置与逐元素调用、链接、内联</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 的 NVIDIA 后端在 LLVM IR 阶段把 libdevice 链接进 kernel 模块。这一步用哪个库文件，什么情况下才链接，拷入多少内容，又怎样影响编译缓存？库路径写错时是什么现象？</t>
+          <t xml:space="preserve">libdevice 的函数体里用编译期查询 __nvvm_reflect 在几种数值写法之间选择。Triton 3.7.1 默认让它在次正规数和 sqrt 两方面各选中哪种写法？在这两个开关上，这相当于 nvcc 的哪组选项？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：默认用 wheel 自带的 libdevice.10.bc；只在模块里有未定义的外部函数时链接，并且只拷入被用到的定义。
-• [T#B#库路径]：默认是已安装的 triton 包下的 backends/nvidia/lib/libdevice.10.bc，可以用环境变量 TRITON_LIBDEVICE_PATH 或启动参数 extern_libs 换掉。
-• [T#B#按需]：没用到 libdevice 的 kernel 整步跳过。链接使用 LinkOnlyNeeded，拷进来的函数被设为 internal，表示只在本模块内使用。
-• [T#B#缓存]：库文件的内容哈希会算进编译缓存键，换一份库就会重新编译。
-[T#B,!c47f17#边界]：路径不存在时，在计算缓存键读取文件的时候就报 FileNotFoundError，比生成任何 IR 都早。官方教程第二段拼出的路径只在 Triton 源码树里存在，在 pip 安装的环境里就会撞上这个错误。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：默认把次正规数清零（flush-to-zero，FTZ），sqrt 用近似指令；在这两个开关上相当于 nvcc 的 --ftz=true 加 --prec-sqrt=false，而不是 nvcc 的默认值。
+• [T#B#reflect]：libdevice 只编译一次，却要服务多种模式，所以用 __nvvm_reflect 写编译期分支；生成 PTX 时这些查询被换成常数，走不到的分支被删掉。
+• [T#B#Triton 的取值]：选项 enable_reflect_ftz 默认为 True，对应 __CUDA_FTZ 为 1；__CUDA_PREC_SQRT 没有人设置，按规则取 0，所以选中近似 sqrt。
+• [T#B#对照 nvcc]：nvcc 默认 --ftz=false、--prec-sqrt=true，即保留次正规数、sqrt 按 IEEE 就近舍入；--use_fast_math 隐含了 --ftz=true 和 --prec-sqrt=false，所以在这两项上也与 Triton 的默认一致。
+[T#B,!c47f17#边界]：反射参数整个模块只有一个值，所有内联进来的函数体一起变；它只影响 libdevice 函数内部的代码，Triton 自己生成的指令不受它影响。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认库 · 按需链接 · 内容哈希进缓存键</t>
+          <t xml:space="preserve">FTZ=1、PREC_SQRT=0 ≈ nvcc --ftz=true --prec-sqrt=false</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 默认库 · 按需链接 · 内容哈希进缓存键</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 编译器前置与逐元素调用、链接、内联</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">libdevice 的函数体里有 __nvvm_reflect("__CUDA_FTZ") 这样的编译期查询。Triton 3.7.1 默认把 libdevice 编成哪种数值模式？这相当于 nvcc 的哪种设置，影响范围有多大？</t>
+          <t xml:space="preserve">只用 NVIDIA 一个后端，把一个调用 libdevice.asin 的 Triton 3.7.1 kernel 与 torch.asin 对照：输入 1e-40（fp32 的次正规数）时 kernel 输出 0，torch.asin 输出 1e-40；其他输入都一致，带绝对容差的常规数值测试也全部通过。原因是什么？怎样让两者一致？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：默认是冲掉次正规数、sqrt 用近似指令。在这两个开关上，它相当于 nvcc 的 use_fast_math，而不是 nvcc 的默认值。
-• [T#B#reflect]：libdevice 只编译一次，却要服务多种模式，所以用 __nvvm_reflect 写编译期分支；生成 PTX 时这些查询被换成常数，走不到的分支被删掉。
-• [T#B#Triton 的取值]：选项 enable_reflect_ftz 默认为 True，对应 __CUDA_FTZ 为 1；__CUDA_PREC_SQRT 没有人设置，按规则取 0，所以选中近似 sqrt。
-• [T#B#对照 nvcc]：nvcc 默认保留次正规数，sqrt 按 IEEE 就近舍入；只有 use_fast_math 才与 Triton 的默认一致。
-[T#B,!c47f17#边界]：反射参数整个模块只有一个值，所有内联进来的函数体一起变；它只影响 libdevice 函数内部的代码，Triton 自己生成的指令不受它影响。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Triton 默认让 libdevice 把次正规数清零（FTZ）；启动 kernel 时传 enable_reflect_ftz=False，结果就与 torch.asin 一致。
+• [T#B#实测]：默认设置下 1e-40 得 0，负输入得 -0；关闭后得 1e-40。分界点在最小的正规数 1.175e-38，从它开始两种设置的结果相同。
+• [T#B#为什么测试没发现]：差值只有 1e-40 量级，远小于常用的绝对容差，要专门用次正规数输入对比才看得出来。
+[T#B,!c47f17#边界]：这只是一台 NVIDIA GPU 上 asin 对几个输入的观察，不能直接推广到其他函数或后端。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTZ=1、PREC_SQRT=0 ≈ use_fast_math</t>
+          <t xml:space="preserve">默认 FTZ：次正规数 → 0；enable_reflect_ftz=False 对齐</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · FTZ=1、PREC_SQRT=0 ≈ use_fast_math</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · GPU 验收、观察与结课前答疑（RTX 4070 Ti 实测）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">测试发现：同一个调用 libdevice.asin 的 Triton 3.7.1 kernel，对输入 1e-40（fp32 的次正规数）输出 0，而 torch.asin 输出 1e-40；其他输入都一致。原因是什么？怎样让两者一致，这个改动的范围有多大？</t>
+          <t xml:space="preserve">常听到一种说法：Triton 里 tl.math 的函数是硬件指令，libdevice 的函数是库调用。在 Triton 3.7.1 的 NVIDIA 后端上，实际编译出来是什么情况？两者真正的区别是什么？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：Triton 默认让 libdevice 把次正规数当作 0；启动 kernel 时传 enable_reflect_ftz=False，结果就与 torch.asin 一致。
-• [T#B#实测]：在 RTX 4070 Ti 上：默认设置下 1e-40 得 0，负数输入得 -0；关闭后得 1e-40。分界点在最小的正规数 1.175e-38，从它开始结果相同。
-• [T#B#为什么平时查不出]：差值只有 1e-40 量级，带绝对容差的常规数值测试发现不了，需要专门用次正规数输入去比较。
-[T#B,!c47f17#边界]：这是编译选项，改了会重新编译，并且只影响这个 kernel 里 libdevice 函数内部的代码。这只是一台设备上对 asin 的观察。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：这个说法不对：tl.math 的大多数函数最后调用的也是 libdevice，生成的 PTX 与直接写 libdevice 的同名函数完全相同。真正的区别是后端中立的写法与点名厂商函数。
+• [T#B#证据示例]：fp32 输入的只编译观察：tl.exp、tl.sqrt_rn、除法和 tl.abs 由后端直接生成指令；tl.log、tl.sin、tl.erf、tl.sqrt、tl.rsqrt、tl.floor、tl.exp2 都被改成 __nv_ 开头的库函数调用，再链接、内联。
+• [T#B#真正的区别]：tl.math 只说要算什么，怎么实现由各后端决定；libdevice 点名要厂商库里的函数，函数多得多，但要确认目标后端实现了它。
+• [T#B#怎样自查]：看链接前的 LLVM IR 里有没有 declare @__nv_* 的声明，就知道某个 tl.math 函数在这个后端上走没走 libdevice。
+[T#B,!c47f17#边界]：清单只是证据示例，不必背。换成 AMD 后端，exp、log、sqrt 不链接任何库，erf、sin 才走它的数学库。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认 ftz：次正规数 → 0</t>
+          <t xml:space="preserve">tl.math 是中立写法，多数也走 libdevice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 默认 ftz：次正规数 → 0</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">有人说：在 Triton 里，tl.math 的函数是硬件指令，libdevice 的函数是库调用。在 Triton 3.7.1 的 NVIDIA 后端上，这个说法对吗？两者真正的区别是什么？</t>
+          <t xml:space="preserve">Triton 3.7.1、NVIDIA 后端、fp32 输入：kernel 里直接写 tl.exp(x)、tl.sqrt(x) 和 a / b，结果与 PyTorch eager 在最后一两位上有差别。要贴近 eager，这三处各应换成什么写法？原来的写法差在哪里？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不对。tl.math 的大多数函数最后调用的也是 libdevice，生成的 PTX 与直接写 libdevice 的同名函数完全相同。
-• [T#B#直接出指令的少数]：本机测到 tl.exp、tl.sqrt_rn、除法和 tl.abs 由后端直接生成指令。
-• [T#B#走 libdevice 的多数]：tl.log、tl.sin、tl.erf、tl.sqrt、tl.rsqrt、tl.floor、tl.exp2 都被改成 __nv_ 开头的库函数调用，再链接、内联。
-• [T#B#真正的区别]：tl.math 是后端中立的写法，kernel 只说要算什么，怎么实现由各后端决定；libdevice 是点名要厂商库里的函数，函数多得多，但要确认目标后端实现了它。
-[T#B,!c47f17#边界]：这是对 fp32 输入的只编译观察。换成 AMD 后端，exp、log、sqrt 不链接任何库，erf、sin 才走它的数学库。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原来的三种写法都是快速档（近似实现）；要贴近 eager，分别换成 libdevice.exp、tl.sqrt_rn 和 tl.div_rn。
+• [T#B#exp]：tl.exp 先乘 log₂e，再做近似的 2 的幂；libdevice.exp 更精确，代价是指令更多（延伸：本机 PTX 里每元素 2 条对 8 条）。
+• [T#B#sqrt]：tl.sqrt 是近似的 sqrt.approx；tl.sqrt_rn 生成按 IEEE 就近舍入的 sqrt.rn。
+• [T#B#除法]：a / b 生成近似的 div.full；tl.div_rn 生成 IEEE 舍入的 div.rn。
+• [T#B#延伸]：PyTorch 2.13 的 Inductor 生成 kernel 时，默认只对 sqrt、exp 用精确写法（tl.sqrt_rn、libdevice.exp）；除法舍入、关闭 ftz、改用 CUDA 工具链的 libdevice 是 eager_numerics 的三个开关，默认都关闭。换 libdevice 的理由是两份库的多项式不同，erf、pow 会差约 1 ulp。
+[T#B,!c47f17#边界]：tl.sqrt_rn 和 tl.div_rn 在 3.7.1 只接受 fp32。精确档的代价来自更多指令或更慢的 IEEE 舍入，三者的实际速度差都没有实测；不要求和 eager 对齐时保留快速档。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tl.math 是中立写法，多数也走 libdevice</t>
+          <t xml:space="preserve">三处默认都是快速档；精确档 libdevice.exp、tl.sqrt_rn、tl.div_rn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · tl.math 是中立写法，多数也走 libdevice</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 的 kernel 算出的结果与 PyTorch eager 相比，在最后一两位上有差别。exp、sqrt 和除法这三个运算，最顺手的写法各属于快速档还是精确档？精确档怎么写？PyTorch 2.13 的 Inductor 是怎么选的？</t>
+          <t xml:space="preserve">一种快速计算 e 的 x 次方的做法是：先算 x 乘 log₂e，再对乘积做 2 的幂。Triton 3.7.1 的 tl.exp 对 fp32 输入就是这样做的。为什么 |x| 越大，结果的相对误差越大？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：三者最顺手的写法都是快速档；要贴近 eager，得主动换成 libdevice.exp、tl.sqrt_rn 和 tl.div_rn。
-• [T#B#exp]：tl.exp 每个元素 2 条指令：先乘 log₂e，再做近似的 2 的幂。libdevice.exp 每个元素 8 条，先把 x 拆成整数和小数部分。
-• [T#B#sqrt]：tl.sqrt 和 libdevice.sqrt 生成近似的 sqrt.approx；tl.sqrt_rn 生成按 IEEE 就近舍入的 sqrt.rn。
-• [T#B#除法]：a / b 和 tl.fdiv 生成近似的 div.full；tl.div_rn 生成 div.rn。
-• [T#B#Inductor]：sqrt 一律生成 tl.sqrt_rn，exp 默认生成 libdevice.exp；eager_numerics 这组开关再控制除法舍入、关闭 ftz，以及改用 CUDA 工具链的 libdevice。
-[T#B,!c47f17#边界]：精确档更慢：exp 的指令数是实测，除法和 sqrt 的速度差没有实测。不要求和 eager 对齐、对最后一两位不敏感时，保留快速档。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：乘积只保留 24 位有效数字，它的舍入误差与乘积的大小成正比；这点误差落在指数上，直接变成结果的相对误差，所以 |x| 越大，结果偏离得越多。
+• [T#B#量级]：CUDA 文档给这类快速 exp 的误差上界随 |x| 线性增长，标准 expf 则是常数 2 ulp。ulp 是浮点数最后一位的一个单位。
+[T#B,!c47f17#边界]：把文档的上界套到 Triton 的 tl.exp 上是推断，没有实测。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认偏快；exp、sqrt、除法各有精确档</t>
+          <t xml:space="preserve">乘积的舍入误差落进指数，随 |x| 变大</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 默认偏快；exp、sqrt、除法各有精确档</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">一种快速计算 e 的 x 次方的做法是：先算 x 乘 log₂e，再对乘积做 2 的幂。Triton 3.7.1 的 tl.exp 对 fp32 输入就是这样做的。为什么 |x| 越大，结果的相对误差越大？更精确的实现怎样避免？</t>
+          <t xml:space="preserve">Triton 3.7.1 的 tl.inline_asm_elementwise 允许在 kernel 里直接写一条目标平台的汇编指令，例如 NVIDIA 的 rsqrt.approx.f32。它进入编译流程的方式和调用 libdevice 有什么不同？因此把同一个 kernel 拿到 AMD 后端编译会怎样？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：乘积只保留 24 位有效数字，丢掉的舍入误差落在指数上，被 2 的幂放大；|x| 越大，乘积越大，这点误差的绝对值也越大。
-• [T#B#精确做法]：先把 x 拆成整数部分和小数部分，整数部分精确地变成 2 的整数次幂，只对范围很小的小数部分做逼近，误差就不随 |x| 增长。
-• [T#B#量级]：CUDA 文档给这类快速 exp 的误差上界是 2 + ⌊|1.173·x|⌋ ulp，标准 expf 是 2 ulp。ulp 是浮点数最后一位的一个单位。
-[T#B,!c47f17#边界]：把文档的上界套到 Triton 的 tl.exp 上是推断，没有实测。</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">乘积的舍入误差被指数放大</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 乘积的舍入误差被指数放大</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton 的 tl.inline_asm_elementwise 允许在 kernel 里直接写一条目标平台的汇编指令，例如 NVIDIA 的 rsqrt.approx.f32。它进入编译流程的方式和调用 libdevice 有什么不同？把同一个 kernel 拿到 AMD 后端编译会怎样？</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：指令文本不经过链接，原样带到最终汇编里；换一个后端，这段文本就不是合法指令，编译在最后一步失败。
 • [T#B#NVIDIA]：在 LLVM IR 里它是一条内联汇编调用，生成的 PTX 中这条指令原样出现。
@@ -306,183 +277,129 @@
 [T#B,!c47f17#边界]：只在需要某条特定硬件指令、并且只面向一个后端时才用它；想保持可移植，优先用 tl.math。</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本原样进汇编，不可移植</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1、NVIDIA 后端：厂商库里没有你要的数学函数，想让 kernel 调用自己提供的实现。需要准备哪两样东西？如果启动时忘了传库文件，会在哪一步失败？</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：一张 dtype 到符号的表，加一个含有这些函数定义的库文件；之后走 Triton 公共的链接、内联流程，和 libdevice 完全相同。忘传库文件时链接阶段不报错，要到最后一步才失败。
+• [T#B#表]：仿照后端实现模块里现成函数的写法，写一个调用 core.extern_elementwise 的函数，为每种参数 dtype 指定符号名和返回类型。
+• [T#B#库文件]：启动 kernel 时用 extern_libs 传入库的名字和路径；文件可以是 bitcode，也可以是文本形式的 LLVM IR。
+• [T#B#名字要对上]：链接只按名字匹配，表里的符号名必须和库文件里的定义同名；忘传库或名字对不上，那条声明都会一直留到最后，由最后一步的汇编报 Unresolved extern function。
+[T#B,!c47f17#边界]：这是 NVIDIA 后端的现象；AMD 后端决定链接哪些库的规则不同，对不上时可能编译成功，却留下一次未解析的调用。</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本原样进汇编，不可移植</t>
+          <t xml:space="preserve">dtype 表 + extern_libs；缺库到最后一步才报错</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 文本原样进汇编，不可移植</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">厂商库里没有你要的数学函数，想让 Triton 3.7.1 的 kernel 调用自己提供的实现。需要准备哪两样东西？它之后走什么流程？如果启动时忘了传库文件，会在哪一步报什么错？</t>
+          <t xml:space="preserve">一个基于 Triton 3.7.1 的新后端加了 libdevice 支持：TTIR 里的符号正确，编译也成功，但最终的机器码里仍有对库函数的真实调用。可能是哪两种原因？看哪个中间产物能把它们分开？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：一张 dtype 到符号的表，加一个含有这些函数定义的库文件；之后走和 libdevice 完全相同的链接、内联。
-• [T#B#表]：用 core.extern_elementwise 写一个函数，为每种参数 dtype 指定符号名和返回类型。
-• [T#B#库文件]：启动 kernel 时用 extern_libs 传入库的名字和路径；文件可以是 bitcode，也可以是文本形式的 LLVM IR。本机用一个手写的 5 行文本 IR 验证过，内联后没有 call。
-• [T#B#忘传的现象]：链接阶段不报错，那条声明一直留到最后，由汇编器报 Unresolved extern function。
-[T#B,!c47f17#边界]：各后端决定链接哪些库的规则不同：AMD 只链接键名出现在某个未定义函数名里的库，键名不匹配时编译不报错，却留下一次未解析的调用。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：要么库函数链接进来了但没有被内联，要么库根本没有链接进来；看链接之后的 LLVM IR 就能区分。
+• [T#B#没有内联]：IR 里这个函数有 define，但没有 alwaysinline 属性（要求在调用处内联的函数属性），或者后端没有运行内联优化。
+• [T#B#没有链接]：IR 里仍然只有 declare。本应在最后一步报找不到定义，只是这个后端的最后一步没有为此报错。AMD 后端就有这种情况：它只链接键名出现在某个未定义函数名里的库，自定义库的键名对不上时编译不报错，留下一次未解析的调用。
+[T#B,!c47f17#边界]：对比 O3 前后的 IR 也能确认是否内联；先看链接后的 IR 更省事，一眼分清两类原因。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dtype 表 + extern_libs；缺库到最后才报错</t>
+          <t xml:space="preserve">看链接后的 IR：define 还是 declare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · dtype 表 + extern_libs；缺库到最后才报错</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">要让一个新的 Triton 后端支持 kernel 里的 libdevice 调用，后端需要提供哪几样东西？每一样漏掉或写错时，各是什么现象？</t>
+          <t xml:space="preserve">同一个调用 libdevice.asin 的 Triton 3.7.1 kernel（BLOCK_SIZE 为 1024，num_warps 为 4），编译目标从 NVIDIA 换成 AMD CDNA3（gfx942）。按编译流水线的顺序说，哪些内容跟着变，哪些机制不变？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：六样：接口模块的映射、实现模块里的函数、每个函数的 dtype 符号表、库文件与默认路径、按需链接、让库函数被内联并把数值开关传给库。
-• [T#B#映射]：get_module_map() 把接口模块指向自己的实现模块；漏掉时空壳函数返回 None，下一行才报错。
-• [T#B#函数]：实现模块里要有被调用的函数；缺失时报 AttributeError。
-• [T#B#符号表]：每个函数一张 dtype 到符号的表；dtype 不在表里时报 KeyError。
-• [T#B#库文件]：提供含定义的库和默认路径，内容哈希计入缓存键；路径不存在时，在生成 IR 之前就报 FileNotFoundError。
-• [T#B#链接]：在生成 LLVM IR 的阶段按需链接，表里的符号名要和库里的定义一致；否则到最后一步才报找不到定义。
-• [T#B#内联与开关]：库函数要能被内联，否则机器码里留下真实调用；次正规数等数值模式也要有办法传给库。
-[T#B,!c47f17#边界]：逐元素拆成标量调用、按名字链接这些机制是 Triton 的公共代码，新后端不用重写，只需要往每一环里填内容。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：机制不变，每一环填进去的内容变：按流水线顺序，符号、每线程元素数、链接的库和次正规数的默认处理都不同。
+• [T#B#符号]：查表得到的是 __ocml_asin_f32，而不是 __nv_asinf。
+• [T#B#元素数]：gfx942 属于 CDNA（gfx9），Triton 3.7.1 给它的 warp 是 64 个线程，所以每线程 1024 ÷ (64 × 4) = 4 个元素、生成 4 次调用；NVIDIA 是 32 个线程、8 个元素。换成 RDNA（gfx10 及以上）时 warp 是 32 个线程，每线程也是 8 个。
+• [T#B#库]：AMD 的默认库是 ocml.bc 和 ockl.bc，这个 kernel 只链接了用到的 ocml.bc。
+• [T#B#次正规数]：这个 kernel 在 AMD 上默认保留次正规数，由 kernel 函数上的属性控制；NVIDIA 默认只在 libdevice 内部清零。
+[T#B,!c47f17#边界]：不变的是逐元素拆成标量调用、按名字链接、内联后没有调用。AMD 一侧只是只编译的观察，没有在真实设备上运行。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">映射 · 函数 · 符号表 · 库 · 链接 · 内联</t>
+          <t xml:space="preserve">机制相同；符号、E（看架构的 warp 大小）、库、次正规数默认不同</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 映射 · 函数 · 符号表 · 库 · 链接 · 内联</t>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 四条实现路线与后端迁移</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个新的 Triton 后端加了 libdevice 支持：TTIR 里的符号正确，编译也成功，但最终的机器码里仍有对库函数的真实调用。可能是哪两种原因？看哪个中间产物能把它们分开？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里，想让半精度输入先升到 fp32 再调用 libdevice。直接写 if x.dtype == tl.bfloat16 并在分支里把 x 转成 fp32，可以编译；但先写 is_bf16 = x.dtype == tl.bfloat16，再写 if is_bf16 做同样的事，就会编译报错。为什么？想先存再用应该怎么写？</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：要么库函数链接进来了但没有被内联，要么库根本没有链接进来；看链接之后的 LLVM IR 就能区分。
-• [T#B#没有内联]：IR 里这个函数有 define，但没有 alwaysinline 属性，或者后端没有运行内联优化。
-• [T#B#没有链接]：IR 里仍然只有 declare。本应在最后一步报找不到定义，只是这个后端的最后一步没有为此报错；AMD 后端上自定义库的键名不匹配时就是这种表现。
-[T#B,!c47f17#边界]：对比 O3 前后的 IR 也能确认是否内联；先看链接后的 IR 更省事，一眼分清两类原因。</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">看链接后的 IR：define 还是 declare</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 看链接后的 IR：define 还是 declare</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同一个调用 libdevice.asin 的 Triton 3.7.1 kernel（BLOCK_SIZE 为 1024，num_warps 为 4），目标从 NVIDIA 换成 AMD。编译流程中哪些内容跟着变，哪些机制不变？</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：机制不变，每一环填进去的内容变：符号、每线程元素数、链接的库和次正规数的默认处理都不同。
-• [T#B#符号]：查表得到的是 __ocml_asin_f32，而不是 __nv_asinf。
-• [T#B#元素数]：AMD 每个 warp 是 64 个线程，所以每线程 4 个元素、生成 4 次调用；NVIDIA 是 8 个。
-• [T#B#库]：AMD 的默认库是 ocml.bc 和 ockl.bc，只链接键名出现在未定义函数名里的那个，这里是 ocml.bc；NVIDIA 把 extern_libs 里的库都交给链接器。
-• [T#B#次正规数]：AMD 默认保留，由 kernel 函数上的属性控制，对应选项 allow_flush_denorm；NVIDIA 默认冲成 0，由反射参数控制。
-[T#B,!c47f17#边界]：不变的是：逐元素拆成标量调用、按名字链接、内联后没有调用。AMD 一侧只是只编译的观察，没有在真实设备上运行。</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机制相同；符号、E、库、次正规数默认不同</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 机制相同；符号、E、库、次正规数默认不同</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里，想让半精度输入先升到 fp32 再调用 libdevice。直接写 if x.dtype == tl.bfloat16 并在分支里把 x 转成 fp32，可以编译；但先写 is_bf16 = x.dtype == tl.bfloat16，再写 if is_bf16 做同样的事，就会编译报错。为什么？想先存再用应该怎么写？</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：普通赋值会把这个 Python 布尔值变成张量，if 随之成为运行期分支；运行期分支不允许同一个变量在两条路径上类型不同。
 • [T#B#编译期分支]：if 的条件是普通布尔值时，编译器当场选定一个分支，另一个分支根本不编译，所以可以在分支里改变 x 的类型。
 • [T#B#运行期分支]：条件是张量时两个分支都要编译，于是报错：x 的初始类型是 bf16，then 分支却把它重新定义成 fp32。
 • [T#B#写法]：加上注解，写成 is_bf16: tl.constexpr = x.dtype == tl.bfloat16，它就保持为编译期常量；这种变量不能再被重新赋值。
-[T#B,!c47f17#边界]：这和 C++ 里 if constexpr 与普通 if 的区别是一回事。另外，判断的是变量当前绑定的值：把 x 转成 fp32 之后再判断 x.dtype，就不再是原来的半精度类型。</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+• [T#B#延伸]：if 判断的是变量当前绑定的值：x = x.to(tl.float32) 之后再写 if x.dtype == tl.bfloat16，条件永远不成立，分支不会执行。要保留原类型的判断，就在覆盖之前把它存成 constexpr，或用另一个变量名存放升精度后的值；写回半精度不用手写，tl.store 会按指针的元素类型自动转换。
+[T#B,!c47f17#边界]：这和 C++ 里 if constexpr 与普通 if 的区别是一回事。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">赋值变张量 → 运行期分支；constexpr 注解</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 赋值变张量 → 运行期分支；constexpr 注解</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同一个 asin，内联之后，NVIDIA 的 libdevice 每个元素用 6 条 fma，AMD 的 ocml 每个元素用 9 条。这说明 AMD 的工作量更大吗？多出的 3 条来自哪里？</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不说明。两家库对同一个数学恒等式各写了一套算法；算上全部算术指令，NVIDIA 约 19 条，AMD 约 17 条。
-• [T#B#合并一步]：算 (1 − |x|) ÷ 2 时，AMD 用一条 fma，NVIDIA 用一条减法加一条乘法。
-• [T#B#多项式]：逼近多项式 AMD 有 6 个系数，NVIDIA 有 5 个；换算的分界点也不同，分别是 0.5 和 0.57。
-• [T#B#最后一步]：NVIDIA 先选好变量，两个分支共用一条 fma；AMD 把两个分支各算一遍，再选结果。
-[T#B,!c47f17#边界]：不同的库用不同的多项式，是同一个 kernel 在不同后端上结果相差最后一位的原因之一。两家的精度目标没有查到文档。</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">写法不同，不是工作量不同</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · 写法不同，不是工作量不同</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 练习：实现、Review 与变式</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">手头没有 GPU，只能把 Triton 3.7.1 的 kernel 编译而不运行。怎样用编译产物验证两件事：半精度输入确实是在 kernel 内部升到 fp32 的，以及 libdevice 的函数被内联了？</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：直接编译 kernel 本身，分别检查 TTIR 里选中的符号和 PTX 里有没有 call。
 • [T#B#升精度]：用半精度的指针类型编译 kernel，不经过包装函数。编译能通过，TTIR 里的符号又是只接受 fp32 的 __nv_asinf，说明查表时参数已经是 fp32，升精度只能发生在 kernel 内部。
@@ -490,14 +407,14 @@
 [T#B,!c47f17#边界]：__nv_asinf 是函数的符号，不是指令。只编译能验证分派和内联，数值是否正确仍然要在真实 GPU 上运行。</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">TTIR 看符号，PTX 看 call</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部函数学习记录 10-05 · TTIR 看符号，PTX 看 call</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部函数学习记录 10-05 · 练习：实现、Review 与变式</t>
         </is>
       </c>
     </row>
